--- a/results/Int Task Remove ACC -0.9/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_1_permute.xlsx
@@ -440,117 +440,117 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8024332456165171</v>
+        <v>0.8188298765362232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8045220376710713</v>
+        <v>0.820473859445592</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.804784622204616</v>
+        <v>0.8191688595870708</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7837459796459258</v>
+        <v>0.8090914235590391</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7837205134734916</v>
+        <v>0.8066832668383275</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7724027805287532</v>
+        <v>0.8156222706393895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.774638521830169</v>
+        <v>0.8153440291257557</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7654761702649425</v>
+        <v>0.8009165935693199</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7466615734321798</v>
+        <v>0.8014123350593739</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7631581826584797</v>
+        <v>0.8006128858832517</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7633404072701206</v>
+        <v>0.8074983729945389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7541878648972393</v>
+        <v>0.7991001952406553</v>
       </c>
     </row>
     <row r="14">
@@ -560,117 +560,117 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7428584363770125</v>
+        <v>0.7864618054573065</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7300476311743678</v>
+        <v>0.779752695169916</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7284428850343794</v>
+        <v>0.779752695169916</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7301985418258302</v>
+        <v>0.7809009365892307</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7249217622591324</v>
+        <v>0.7849687331994002</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7251784990049329</v>
+        <v>0.7937607877536006</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7237480546673836</v>
+        <v>0.8048198975693953</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7274415928619262</v>
+        <v>0.8007109778067023</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7119091140601568</v>
+        <v>0.794671910811805</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7009892193203362</v>
+        <v>0.7968272921913169</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6877434141648511</v>
+        <v>0.7803287965818737</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6791982871641059</v>
+        <v>0.7733512539731945</v>
       </c>
     </row>
     <row r="26">
@@ -680,647 +680,647 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6935214057327184</v>
+        <v>0.7769191590503948</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6695477396413985</v>
+        <v>0.7734235024475822</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6845648585684239</v>
+        <v>0.7854740952434849</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6921949011063637</v>
+        <v>0.7435360252020788</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.693307867160899</v>
+        <v>0.7435360252020788</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6835245182649048</v>
+        <v>0.7435360252020788</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6467008102015601</v>
+        <v>0.7443139696103676</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6047218056459447</v>
+        <v>0.7455386095469851</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.621480810767475</v>
+        <v>0.7337721060524602</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.638128142006923</v>
+        <v>0.7399188855248389</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6207537987040548</v>
+        <v>0.7495711307923753</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.620971298680475</v>
+        <v>0.7426150929515294</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6235264046480481</v>
+        <v>0.7242570008394404</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6342229516237043</v>
+        <v>0.7303528479669505</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6291421672655934</v>
+        <v>0.7218939286758534</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6146128670194203</v>
+        <v>0.7154140139403714</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.60357922337606</v>
+        <v>0.694199183196099</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6044316799185082</v>
+        <v>0.6613844165888534</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5944229082368919</v>
+        <v>0.6760489705063996</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5957533742678476</v>
+        <v>0.6777282287805476</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5918208313290512</v>
+        <v>0.6776322118785547</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5906471237373023</v>
+        <v>0.6678937589013705</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5957867632494835</v>
+        <v>0.6663046697414712</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6113250898389972</v>
+        <v>0.6690263433405959</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6504394329532271</v>
+        <v>0.6638612376559803</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6505001744904407</v>
+        <v>0.6682895220848306</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6532120388972205</v>
+        <v>0.6763115550399441</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6532120388972205</v>
+        <v>0.6763115550399441</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6674651726512172</v>
+        <v>0.6757961951652001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6505648774322552</v>
+        <v>0.6761351782160474</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6305569546230535</v>
+        <v>0.660189204229271</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6274002810710884</v>
+        <v>0.6632949454363676</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6133942635088613</v>
+        <v>0.6753630815955028</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6079156409458325</v>
+        <v>0.6753630815955028</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6079156409458325</v>
+        <v>0.6560153928864492</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6325887779066807</v>
+        <v>0.6583235713005668</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5547673617988549</v>
+        <v>0.6571342067287287</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5514188430812182</v>
+        <v>0.6605338464295483</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5514188430812182</v>
+        <v>0.6643449062939174</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5644529960480273</v>
+        <v>0.6592445035511163</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5630599020967149</v>
+        <v>0.650928760740594</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5592584627863766</v>
+        <v>0.6295060505739321</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5771638229440782</v>
+        <v>0.6011057977985909</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5795406657046113</v>
+        <v>0.5399181309715816</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5690536958961735</v>
+        <v>0.5271914584571272</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5690536958961735</v>
+        <v>0.5500072625751016</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5469630174584761</v>
+        <v>0.5165573507635135</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5361423464719919</v>
+        <v>0.5176350414532696</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5117040642124822</v>
+        <v>0.5007132414664742</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5157620516303066</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5163792761947879</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5123565641417428</v>
+        <v>0.5002782415136339</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5239625364307745</v>
+        <v>0.5002782415136339</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4838212463333428</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4979489356083114</v>
+        <v>0.4999392584627864</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4910751440725126</v>
+        <v>0.4999392584627864</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4910751440725126</v>
+        <v>0.4999392584627864</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.493785122096149</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5206804183997812</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5269211397526952</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5132441074106562</v>
+        <v>0.5002782415136339</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.512421078445243</v>
+        <v>0.5002782415136339</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5131343199117173</v>
+        <v>0.4998785169255728</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5058921177480358</v>
+        <v>0.4996002754119389</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5042736010111014</v>
+        <v>0.4992612923610915</v>
       </c>
     </row>
   </sheetData>
